--- a/tests/ExcelRenderer.Formulas.Tests/Fixtures/Oracle/Mapping/mapping-1.xlsx
+++ b/tests/ExcelRenderer.Formulas.Tests/Fixtures/Oracle/Mapping/mapping-1.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" r:id="R0b835b3e387f42b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="2" r:id="Rf0e7b0421c9a4b76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="Rbc399fb77c0f47e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" r:id="Rd9af2d88bf114af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="2" r:id="Rc5ccf610a7e7470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R5f80be8cd56a459b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Amounts">Invoice!$D$1:$D$2</x:definedName>
